--- a/TEST CASES.xlsx
+++ b/TEST CASES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\PARTH CAREER\GIT TASK\16 MARCH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC6C312-4A3D-493D-A9DB-B52D32FDE6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2279C912-BF15-4462-9139-F9984292C1E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -226,7 +226,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -237,6 +237,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -278,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -291,6 +299,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -572,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.7109375" customWidth="1"/>
@@ -919,60 +930,91 @@
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
+    <row r="19" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
     </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="29" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
